--- a/data/employees/EMP076/AST-EMP076-06.xlsx
+++ b/data/employees/EMP076/AST-EMP076-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Budget Tracker - Avery Wilson (Finance)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Avery Wilson | Role: Analyst | Location: Austin | Date: 2025-03-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp076 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>86</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp076 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>77</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Cost Centre</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Budget ($K)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Actual ($K)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Variance ($K)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Variance %</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp076 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>87</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CC-1001 Engineering</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2500</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2380</v>
-      </c>
-      <c r="D5" t="n">
-        <v>120</v>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ast Emp076 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>4.8</v>
+        <v>83</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Section 1: Data quality remediation. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CC-1002 Operations</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1800</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1920</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-120</v>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ast Emp076 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>-6.7</v>
+        <v>95</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Section 1: Department KPI performance. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CC-1003 R&amp;D</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3200</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3100</v>
-      </c>
-      <c r="D7" t="n">
-        <v>100</v>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ast Emp076 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>3.1</v>
+        <v>98</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Section 1: Fabric semantic model planning. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CC-1004 IT</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1195</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5</v>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ast Emp076 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>0.4</v>
+        <v>91</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>On Track</t>
+          <t>Section 1: Department KPI performance. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp076 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>85</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp076 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>72</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp076 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>93</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp076 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>97</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp076 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>79</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp076 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>77</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp076 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>72</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp076 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>81</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp076 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>97</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp076 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>85</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp076 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>73</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp076 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>74</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp076 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>93</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp076 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>68</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp076 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>89</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp076 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>68</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp076 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>80</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP076</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP076 contributes to ast emp076 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>